--- a/Class-6, Student Data-Main File-2026/S-A.xlsx
+++ b/Class-6, Student Data-Main File-2026/S-A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WLP Document\Student Data-Main File-2026\Class-6, Student Data-Main File-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6F71D9-8602-4AD7-BBAC-B5ECD8F292A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858ABDBB-6F37-4036-B96F-5E074A610244}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1747,7 +1747,7 @@
         <v>64</v>
       </c>
       <c r="D33" s="5">
-        <v>171783623</v>
+        <v>1718783623</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
